--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/维保策略表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/维保策略表.xlsx
@@ -513,7 +513,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -560,7 +564,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -889,11 +897,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -940,11 +944,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
